--- a/MATH/M03/bus123-math-m03-l01-starter.xlsx
+++ b/MATH/M03/bus123-math-m03-l01-starter.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R27080a89b4f64218"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R91dd4175f5904f2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R71dbe2cd31584c05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R94f4f38ccd5e4325"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Quotes" sheetId="5" r:id="R03af1c3499ac4f97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Re6e098c3d8f34e3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R03f6d0b62ea54059"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rf8122bb45fe1478f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R06e34f0b90f04e27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Quotes" sheetId="5" r:id="R3e583bb9c5c74344"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1532,22 +1532,15 @@
         <x:v>One rate with the same pricing effect</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="42" customHeight="1">
-      <x:c r="A11" s="64" t="str">
-        <x:v>Difference from adding rates</x:v>
-      </x:c>
+    <x:row r="11" customHeight="1" hidden="1">
+      <x:c r="A11" s="64"/>
       <x:c r="B11" s="51"/>
       <x:c r="C11" s="60"/>
       <x:c r="D11" s="51"/>
       <x:c r="E11" s="51"/>
       <x:c r="F11" s="76"/>
-      <x:c r="G11" s="69" t="str">
-        <x:f>IF(F11="","Enter a formula, then check.",IF(ROUND(F11,2)=ROUND(B9*(1-C9)*(1-D9)*(1-E9)-B9*(1-SUM(C9:E9)),2),"Correct - shortcut difference is $11.28.","Try again - compare chain price with the added-rates price."))</x:f>
-        <x:v>Enter a formula, then check.</x:v>
-      </x:c>
-      <x:c r="H11" s="71" t="str">
-        <x:v>Cost of using the invalid shortcut</x:v>
-      </x:c>
+      <x:c r="G11" s="69"/>
+      <x:c r="H11" s="71"/>
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="65"/>
@@ -1561,7 +1554,7 @@
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="64" t="str">
-        <x:v>Cash discount amount · slide 17</x:v>
+        <x:v>Cash discount amount · slide 18</x:v>
       </x:c>
       <x:c r="B13" s="72" t="n">
         <x:v>3750</x:v>
@@ -1635,8 +1628,8 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B17" s="27" t="str">
-        <x:f>COUNTIF(G5:G15,"Correct*")&amp;" of 9 complete"</x:f>
-        <x:v>0 of 9 complete</x:v>
+        <x:f>COUNTIF(G5:G15,"Correct*")&amp;" of 8 complete"</x:f>
+        <x:v>0 of 8 complete</x:v>
       </x:c>
       <x:c r="C17" s="28"/>
       <x:c r="D17" s="28"/>

--- a/MATH/M03/bus123-math-m03-l01-starter.xlsx
+++ b/MATH/M03/bus123-math-m03-l01-starter.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Re6e098c3d8f34e3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R03f6d0b62ea54059"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="Rf8122bb45fe1478f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="R06e34f0b90f04e27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Quotes" sheetId="5" r:id="R3e583bb9c5c74344"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rdec66cf6a1a04c9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="2" r:id="R72d87fdfecf94b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class Challenge" sheetId="3" r:id="R30eec5e5e55c4f7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FormulaReferenceCard" sheetId="4" r:id="Rccb19a1ccefe402d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vendor Quotes" sheetId="5" r:id="R34b0c6e399424764"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -98,9 +98,6 @@
     <x:t xml:space="preserve">Vendor Quote Comparison: build the linked model in class, then finish the purchasing recommendation for homework.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">HOW: use formulas and cell references  ·  TIME: 15 minutes in class + finish for homework  ·  DELIVERABLE: completed model, quote choice, and 2-sentence recommendation</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Required Units</x:t>
   </x:si>
   <x:si>
@@ -183,12 +180,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Cost Basis for Recommendation</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Control Total — All Final Costs</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Recommendation Explanation</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Formula Reference Card — Vendor Quote Comparison</x:t>
@@ -1532,7 +1523,7 @@
         <x:v>One rate with the same pricing effect</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" customHeight="1" hidden="1">
+    <x:row r="11" hidden="1" customHeight="1">
       <x:c r="A11" s="64"/>
       <x:c r="B11" s="51"/>
       <x:c r="C11" s="60"/>
@@ -1703,8 +1694,8 @@
       <x:c r="L2" s="24"/>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
-      <x:c r="A3" s="31" t="s">
-        <x:v>28</x:v>
+      <x:c r="A3" s="31" t="str">
+        <x:v>HOW: use formulas and cell references  ·  TIME: 15 minutes in class + finish for homework  ·  DELIVERABLE: completed model, quote choice, and brief recommendation explanation</x:v>
       </x:c>
       <x:c r="B3" s="31"/>
       <x:c r="C3" s="31"/>
@@ -1720,17 +1711,17 @@
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="12" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="13"/>
       <x:c r="C5" s="12" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="32" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B6" s="32"/>
       <x:c r="C6" s="32"/>
@@ -1746,34 +1737,34 @@
     </x:row>
     <x:row r="7" ht="36" customHeight="1">
       <x:c r="A7" s="8" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B7" s="8" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="s">
+      <x:c r="C7" s="8" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C7" s="8" t="s">
+      <x:c r="D7" s="8" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D7" s="8" t="s">
+      <x:c r="E7" s="8" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="s">
+      <x:c r="F7" s="8" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="s">
+      <x:c r="G7" s="8" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G7" s="8" t="s">
+      <x:c r="H7" s="8" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H7" s="8" t="s">
+      <x:c r="I7" s="8" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="I7" s="8" t="s">
+      <x:c r="J7" s="8" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="J7" s="8" t="s">
-        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="25" customHeight="1">
@@ -1839,7 +1830,7 @@
     <x:row r="13" ht="25" customHeight="1"/>
     <x:row r="14" ht="25" customHeight="1">
       <x:c r="A14" s="32" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B14" s="32"/>
       <x:c r="C14" s="32"/>
@@ -1856,40 +1847,40 @@
     <x:row r="15" ht="25" customHeight="1"/>
     <x:row r="16" ht="40" customHeight="1">
       <x:c r="A16" s="8" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B16" s="8" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B16" s="8" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="C16" s="8" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D16" s="8" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D16" s="8" t="s">
+      <x:c r="E16" s="8" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="E16" s="8" t="s">
+      <x:c r="F16" s="8" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="F16" s="8" t="s">
+      <x:c r="G16" s="8" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="G16" s="8" t="s">
+      <x:c r="H16" s="8" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="H16" s="8" t="s">
+      <x:c r="I16" s="8" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="I16" s="8" t="s">
+      <x:c r="J16" s="8" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="J16" s="8" t="s">
+      <x:c r="K16" s="8" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="K16" s="8" t="s">
+      <x:c r="L16" s="8" t="s">
         <x:v>51</x:v>
-      </x:c>
-      <x:c r="L16" s="8" t="s">
-        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="25" customHeight="1">
@@ -1965,7 +1956,7 @@
     <x:row r="22" ht="25" customHeight="1"/>
     <x:row r="23" ht="25" customHeight="1">
       <x:c r="A23" s="33" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B23" s="33"/>
       <x:c r="C23" s="33"/>
@@ -1982,58 +1973,62 @@
     <x:row r="24" ht="25" customHeight="1"/>
     <x:row r="25" ht="34" customHeight="1">
       <x:c r="A25" s="17" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B25" s="18"/>
+      <x:c r="C25"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
       <x:c r="A26" s="17" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B26" s="19"/>
+      <x:c r="C26"/>
     </x:row>
     <x:row r="27" ht="34" customHeight="1">
       <x:c r="A27" s="17" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B27" s="18"/>
+      <x:c r="C27"/>
     </x:row>
     <x:row r="28" ht="34" customHeight="1">
-      <x:c r="A28" s="17" t="s">
-        <x:v>57</x:v>
+      <x:c r="A28" s="17" t="str">
+        <x:v>Check</x:v>
       </x:c>
       <x:c r="B28" s="18"/>
     </x:row>
-    <x:row r="29" ht="58" customHeight="1">
-      <x:c r="A29" s="17" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B29" s="34"/>
-      <x:c r="C29" s="34"/>
-      <x:c r="D29" s="34"/>
-      <x:c r="E29" s="34"/>
-      <x:c r="F29" s="34"/>
-      <x:c r="G29" s="34"/>
-      <x:c r="H29" s="34"/>
-      <x:c r="I29" s="34"/>
-      <x:c r="J29" s="34"/>
-      <x:c r="K29" s="34"/>
-      <x:c r="L29" s="34"/>
-    </x:row>
-    <x:row r="30" ht="58" customHeight="1">
-      <x:c r="B30" s="34"/>
-      <x:c r="C30" s="34"/>
-      <x:c r="D30" s="34"/>
-      <x:c r="E30" s="34"/>
-      <x:c r="F30" s="34"/>
-      <x:c r="G30" s="34"/>
-      <x:c r="H30" s="34"/>
-      <x:c r="I30" s="34"/>
-      <x:c r="J30" s="34"/>
-      <x:c r="K30" s="34"/>
-      <x:c r="L30" s="34"/>
-    </x:row>
-    <x:row r="31" ht="58" customHeight="1">
+    <x:row r="29" ht="15" customHeight="1">
+      <x:c r="A29"/>
+      <x:c r="B29"/>
+      <x:c r="C29"/>
+      <x:c r="D29"/>
+      <x:c r="E29"/>
+      <x:c r="F29"/>
+      <x:c r="G29"/>
+      <x:c r="H29"/>
+      <x:c r="I29"/>
+      <x:c r="J29"/>
+      <x:c r="K29"/>
+      <x:c r="L29"/>
+    </x:row>
+    <x:row r="30" ht="15" customHeight="1">
+      <x:c r="B30"/>
+      <x:c r="C30"/>
+      <x:c r="D30"/>
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="G30"/>
+      <x:c r="H30"/>
+      <x:c r="I30"/>
+      <x:c r="J30"/>
+      <x:c r="K30"/>
+      <x:c r="L30"/>
+    </x:row>
+    <x:row r="31" ht="34" customHeight="1">
+      <x:c r="A31" s="17" t="str">
+        <x:v>Recommendation Explanation</x:v>
+      </x:c>
       <x:c r="B31" s="34"/>
       <x:c r="C31" s="34"/>
       <x:c r="D31" s="34"/>
@@ -2046,15 +2041,17 @@
       <x:c r="K31" s="34"/>
       <x:c r="L31" s="34"/>
     </x:row>
+    <x:row r="32" ht="58" customHeight="1"/>
+    <x:row r="33" ht="58" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A23:L23"/>
-    <x:mergeCell ref="B29:L31"/>
     <x:mergeCell ref="A1:L1"/>
     <x:mergeCell ref="A2:L2"/>
     <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A14:L14"/>
+    <x:mergeCell ref="B31:L33"/>
   </x:mergeCells>
   <x:dataValidations count="1">
     <x:dataValidation type="whole" sqref="B26">
@@ -2078,7 +2075,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="23" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B1" s="23"/>
       <x:c r="C1" s="23"/>
@@ -2086,7 +2083,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="24" t="s">
-        <x:v>60</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B2" s="24"/>
       <x:c r="C2" s="24"/>
@@ -2095,170 +2092,170 @@
     <x:row r="3" ht="31.5" customHeight="1"/>
     <x:row r="4" ht="36" customHeight="1">
       <x:c r="A4" s="8" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="B4" s="8" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="s">
-        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="36" customHeight="1">
       <x:c r="A5" s="6" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D5" s="21" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="B5" s="20" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D5" s="21" t="s">
-        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="36" customHeight="1">
       <x:c r="A6" s="6" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D6" s="21" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="B6" s="20" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D6" s="21" t="s">
-        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="36" customHeight="1">
       <x:c r="A7" s="6" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D7" s="21" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="B7" s="20" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D7" s="21" t="s">
-        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="36" customHeight="1">
       <x:c r="A8" s="6" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="s">
         <x:v>77</x:v>
-      </x:c>
-      <x:c r="B8" s="20" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="C8" s="6" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D8" s="21" t="s">
-        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
       <x:c r="A9" s="6" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="B9" s="20" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="D9" s="21" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="36" customHeight="1">
       <x:c r="A10" s="6" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B10" s="20" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D10" s="21" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="B10" s="20" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="C10" s="6" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D10" s="21" t="s">
-        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
       <x:c r="A11" s="6" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B11" s="20" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D11" s="21" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="B11" s="20" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D11" s="21" t="s">
-        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="36" customHeight="1">
       <x:c r="A12" s="6" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B12" s="20" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D12" s="21" t="s">
         <x:v>93</x:v>
-      </x:c>
-      <x:c r="B12" s="20" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="D12" s="21" t="s">
-        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
       <x:c r="A13" s="6" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D13" s="21" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="B13" s="20" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="C13" s="6" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D13" s="21" t="s">
-        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
       <x:c r="A14" s="6" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B14" s="20" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D14" s="21" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="B14" s="20" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C14" s="6" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D14" s="21" t="s">
-        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="36" customHeight="1">
       <x:c r="A15" s="6" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B15" s="20" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D15" s="21" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="B15" s="20" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="C15" s="6" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="D15" s="21" t="s">
-        <x:v>108</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2286,7 +2283,7 @@
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
       <x:c r="A1" s="23" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B1" s="23"/>
       <x:c r="C1" s="23"/>
@@ -2301,7 +2298,7 @@
     </x:row>
     <x:row r="2" ht="28" customHeight="1">
       <x:c r="A2" s="24" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B2" s="24"/>
       <x:c r="C2" s="24"/>
@@ -2316,7 +2313,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="33" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B3" s="33"/>
       <x:c r="C3" s="33"/>
@@ -2331,7 +2328,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="3" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B4" s="7">
         <x:v>50</x:v>
@@ -2339,7 +2336,7 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="3" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B5" s="7">
         <x:v>10</x:v>
@@ -2347,45 +2344,45 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="3" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
       <x:c r="A8" s="8" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="s">
+      <x:c r="C8" s="8" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C8" s="8" t="s">
+      <x:c r="D8" s="8" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D8" s="8" t="s">
+      <x:c r="E8" s="8" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E8" s="8" t="s">
+      <x:c r="F8" s="8" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="F8" s="8" t="s">
+      <x:c r="G8" s="8" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="G8" s="8" t="s">
+      <x:c r="H8" s="8" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="H8" s="8" t="s">
+      <x:c r="I8" s="8" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="I8" s="8" t="s">
+      <x:c r="J8" s="8" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="J8" s="8" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="K8" s="8" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
@@ -2393,7 +2390,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="11" t="s">
-        <x:v>117</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C9" s="11">
         <x:v>50</x:v>
@@ -2420,7 +2417,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="K9" s="4" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
@@ -2428,7 +2425,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="11" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C10" s="11">
         <x:v>60</x:v>
@@ -2455,7 +2452,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="K10" s="4" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
@@ -2463,7 +2460,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C11" s="11">
         <x:v>40</x:v>
@@ -2490,7 +2487,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="K11" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
@@ -2498,7 +2495,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B12" s="11" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C12" s="11">
         <x:v>55</x:v>
@@ -2525,7 +2522,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="K12" s="4" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
@@ -2533,7 +2530,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B13" s="11" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C13" s="11">
         <x:v>50</x:v>
@@ -2560,12 +2557,12 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="K13" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
       <x:c r="A15" s="35" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B15" s="35"/>
       <x:c r="C15" s="35"/>
